--- a/manuscript_material/source_data/Source_Data_Fig1.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig1.xlsx
@@ -425,12 +425,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -467,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>agent_traces</t>
+          <t>execution_traces</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
